--- a/output/核心业务系统风险对照.xlsx
+++ b/output/核心业务系统风险对照.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +69,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +461,493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:N15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>支付网关</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>电商平台</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>OA系统</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.11</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>支付数据库未授权访问漏洞</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.2.20</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>商城应用SQL注入漏洞</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.31</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>OA数据库弱鉴权漏洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.1.10</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>支付接口存在异常登录行为</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.2.21</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>商城缓存越权访问漏洞</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>10.10.3.31</t>
+        </is>
+      </c>
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="M4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>OA数据库发现可疑访问</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10.10.2.20</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>商城应用出现高危扫描行为</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>10.10.2.21</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>Redis 弱密码</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="L12" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="L13" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="L14" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/核心业务系统风险对照.xlsx
+++ b/output/核心业务系统风险对照.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,16 +25,43 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+        <bgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +69,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +461,422 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="32" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>业务系统3</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>业务系统1</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="n"/>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>10.248.38.136</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索攻击攻击活动—Web应用漏洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>192.168.254.90</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>检测到银狐病毒活动—数据窃取</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>文件上传漏洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>目录遍历漏洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Spring Boot Actuator未授权访问漏洞</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索攻击攻击活动—WebShell上传</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>192.168.100.200</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>检测到银狐病毒活动—病毒木马行为</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="F1:I1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/output/核心业务系统风险对照.xlsx
+++ b/output/核心业务系统风险对照.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -472,12 +472,20 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="32" customWidth="1" min="14" max="14"/>
+    <col width="15" customWidth="1" min="16" max="16"/>
+    <col width="8" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="32" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>业务系统3</t>
+          <t>业务系统2</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -491,6 +499,22 @@
       <c r="G1" s="2" t="n"/>
       <c r="H1" s="2" t="n"/>
       <c r="I1" s="2" t="n"/>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>业务系统3</t>
+        </is>
+      </c>
+      <c r="L1" s="2" t="n"/>
+      <c r="M1" s="2" t="n"/>
+      <c r="N1" s="2" t="n"/>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>业务系统4</t>
+        </is>
+      </c>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -533,348 +557,966 @@
           <t>名称</t>
         </is>
       </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>IP</t>
+        </is>
+      </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>检测到银狐攻击攻击活动—勒索软件活动</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>192.168.200.22</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Microsoft Exchange Server远程代码执行漏洞(CVE-2021-34473)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>漏洞</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Apache Log4j2远程代码执行漏洞(CVE-2021-44228)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>10.248.38.136</t>
-        </is>
-      </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>严重</t>
-        </is>
-      </c>
-      <c r="H3" s="5" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>检测到勒索攻击攻击活动—Web应用漏洞</t>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>192.168.200.33</t>
+        </is>
+      </c>
+      <c r="Q3" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="R3" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>检测到响尾蛇APT攻击攻击活动—DNS隧道</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>检测到海莲花APT攻击攻击活动—端口扫描</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>192.168.200.22</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>Microsoft Exchange服务器端请求伪造漏洞(CVE-2021-27065)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>漏洞</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>代码执行</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>192.168.254.90</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>低危</t>
-        </is>
-      </c>
-      <c r="H4" s="5" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>检测到银狐病毒活动—数据窃取</t>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>目录遍历漏洞</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>172.17.75.124</t>
+        </is>
+      </c>
+      <c r="Q4" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="R4" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索病毒活动—WebShell上传</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>192.168.100.205</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>检测到摩诃草APT攻击活动—病毒木马行为</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>10.248.38.136</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索攻击攻击活动—Web应用漏洞</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>漏洞</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>文件上传漏洞</t>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>Spring Boot Actuator未授权访问漏洞</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>192.168.118.232</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>检测到蠕虫病毒活动—CobaltStrike</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索攻击攻击活动—WebShell上传</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>192.168.200.22</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>检测到cobaltstrike远控攻击活动—SQL注入漏洞</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>漏洞</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>目录遍历漏洞</t>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>代码执行</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>172.20.64.95</t>
+        </is>
+      </c>
+      <c r="Q6" s="5" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="R6" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>检测到后门木马活动—横向移动</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>检测到银狐攻击攻击活动—DNS隧道</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>168.196.23.21</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>检测到挖矿病毒活动—数据窃取</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>漏洞</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Spring Boot Actuator未授权访问漏洞</t>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>文件上传漏洞</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>192.168.100.200</t>
+          <t>192.168.213.156</t>
         </is>
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>检测到海莲花APT攻击攻击活动—远程代码执行</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>192.168.254.90</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>检测到银狐病毒活动—数据窃取</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>10.245.224.255</t>
+        </is>
+      </c>
+      <c r="L8" s="5" t="inlineStr">
+        <is>
           <t>中危</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>检测到勒索攻击攻击活动—WebShell上传</t>
+      <c r="M8" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>检测到cobaltstrike远控攻击活动—CobaltStrike</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>检测到响尾蛇APT攻击攻击活动—蠕虫传播</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>192.168.50.10</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>检测到下载者木马活动—数据窃取</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
           <t>192.168.100.200</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>高危</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>事件</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>检测到银狐病毒活动—病毒木马行为</t>
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>192.168.213.156</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>检测到摩诃草APT攻击活动—DNS隧道</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>10.245.224.255</t>
+        </is>
+      </c>
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="M10" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>检测到下载者木马活动—蠕虫传播</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>总数</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>总数</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>2</v>
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>192.168.24.241</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>检测到后门木马活动—文件上传漏洞</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>10.18.20.115</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>检测到挖矿病毒活动—后门程序</t>
+        </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>10.16.11.65</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>检测到勒索病毒活动—系统漏洞攻击</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>10.100.1.50</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>高危</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>中危</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>检测到蠕虫病毒活动—命令注入</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>总数</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>低危</t>
+          <t>总数</t>
         </is>
       </c>
       <c r="G15" s="7" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="L15" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>总数</t>
+        </is>
+      </c>
+      <c r="Q15" s="7" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>漏洞</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>漏洞</t>
+          <t>严重</t>
         </is>
       </c>
       <c r="G16" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="L16" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>严重</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>高危</t>
         </is>
       </c>
       <c r="G17" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>高危</t>
+        </is>
+      </c>
+      <c r="Q17" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>弱口令</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>弱口令</t>
+          <t>中危</t>
         </is>
       </c>
       <c r="G18" s="7" t="n">
         <v>0</v>
       </c>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>中危</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>低危</t>
+        </is>
+      </c>
+      <c r="Q19" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>漏洞</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="Q21" s="7" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>弱口令</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
+    <mergeCell ref="K1:N1"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="P1:S1"/>
     <mergeCell ref="F1:I1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
